--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.45039964909611</v>
+        <v>8.360689942978119</v>
       </c>
       <c r="D2" t="n">
-        <v>11.58768522027225</v>
+        <v>1.88299884829424</v>
       </c>
       <c r="E2" t="n">
-        <v>7.845709448366715</v>
+        <v>1.274927785359592</v>
       </c>
       <c r="F2" t="n">
-        <v>11.78141628820408</v>
+        <v>1.914480146833162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.64530111811081</v>
+        <v>4.654861431693007</v>
       </c>
       <c r="D3" t="n">
-        <v>8.882498245266385</v>
+        <v>1.443405964855788</v>
       </c>
       <c r="E3" t="n">
-        <v>7.845709448366715</v>
+        <v>1.274927785359592</v>
       </c>
       <c r="F3" t="n">
-        <v>11.78141628820408</v>
+        <v>1.914480146833162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.17524465719604</v>
+        <v>5.878477256794357</v>
       </c>
       <c r="D4" t="n">
-        <v>35.17526202629853</v>
+        <v>5.71598007927351</v>
       </c>
       <c r="E4" t="n">
-        <v>7.845709448366715</v>
+        <v>1.274927785359592</v>
       </c>
       <c r="F4" t="n">
-        <v>11.78141628820408</v>
+        <v>1.914480146833162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.0086188333019</v>
+        <v>6.176400560411558</v>
       </c>
       <c r="D5" t="n">
-        <v>29.6080949185106</v>
+        <v>4.811315424257972</v>
       </c>
       <c r="E5" t="n">
-        <v>7.845709448366715</v>
+        <v>1.274927785359592</v>
       </c>
       <c r="F5" t="n">
-        <v>11.78141628820408</v>
+        <v>1.914480146833162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.40010325051553</v>
+        <v>7.377516778208774</v>
       </c>
       <c r="D6" t="n">
-        <v>36.47661446430819</v>
+        <v>5.927449850450081</v>
       </c>
       <c r="E6" t="n">
-        <v>7.845709448366715</v>
+        <v>1.274927785359592</v>
       </c>
       <c r="F6" t="n">
-        <v>11.78141628820408</v>
+        <v>1.914480146833162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
